--- a/penca_data_source.xlsx
+++ b/penca_data_source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395AEE4C-8A93-496F-85EE-213190BEAB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13F5EFF-07F5-4DE2-A5BD-C20E5B7A587C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,11 @@
     <sheet name="DATA_GRUPOS" sheetId="1" r:id="rId1"/>
     <sheet name="DATA_FINAL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="75">
   <si>
     <t>ID_PARTIDO</t>
   </si>
@@ -42,6 +45,9 @@
     <t>TIPO</t>
   </si>
   <si>
+    <t>GRUPO</t>
+  </si>
+  <si>
     <t>EQUIPO_1</t>
   </si>
   <si>
@@ -63,7 +69,184 @@
     <t>PROCESADO</t>
   </si>
   <si>
-    <t>GRUPO</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>Corea del Sur</t>
+  </si>
+  <si>
+    <t>Rep. Checa</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>Bosnia</t>
+  </si>
+  <si>
+    <t>Catar</t>
+  </si>
+  <si>
+    <t>Suiza</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Marruecos</t>
+  </si>
+  <si>
+    <t>Haití</t>
+  </si>
+  <si>
+    <t>Escocia</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>EE. UU.</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Turquía</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>Curazao</t>
+  </si>
+  <si>
+    <t>Costa de Marfil</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Países Bajos</t>
+  </si>
+  <si>
+    <t>Japón</t>
+  </si>
+  <si>
+    <t>Suecia</t>
+  </si>
+  <si>
+    <t>Túnez</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Egipto</t>
+  </si>
+  <si>
+    <t>Irán</t>
+  </si>
+  <si>
+    <t>Nueva Zelanda</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Cabo Verde</t>
+  </si>
+  <si>
+    <t>Arabia Saudita</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Irak</t>
+  </si>
+  <si>
+    <t>Noruega</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Argelia</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Jordania</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>RD Congo</t>
+  </si>
+  <si>
+    <t>Uzbekistán</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Inglaterra</t>
+  </si>
+  <si>
+    <t>Croacia</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Panamá</t>
   </si>
   <si>
     <t>FASE</t>
@@ -79,42 +262,6 @@
   </si>
   <si>
     <t>TBD</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>L</t>
   </si>
 </sst>
 </file>
@@ -133,6 +280,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -149,7 +297,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -183,6 +331,19 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -226,18 +387,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,8 +711,9 @@
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -557,29 +724,29 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -587,15 +754,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4">
+        <v>46184</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J2">
         <v>0</v>
       </c>
@@ -605,15 +782,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="4">
+        <v>46185</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="J3">
         <v>0</v>
       </c>
@@ -623,15 +810,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4">
+        <v>46191</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="J4">
         <v>0</v>
       </c>
@@ -641,15 +838,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4">
+        <v>46192</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J5">
         <v>0</v>
       </c>
@@ -659,15 +866,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4">
+        <v>46197</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="J6">
         <v>0</v>
       </c>
@@ -677,15 +894,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="4">
+        <v>46197</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="J7">
         <v>0</v>
       </c>
@@ -695,15 +922,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="4">
+        <v>46185</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J8">
         <v>0</v>
       </c>
@@ -713,15 +950,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="4">
+        <v>46186</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J9">
         <v>0</v>
       </c>
@@ -731,15 +978,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="4">
+        <v>46191</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J10">
         <v>0</v>
       </c>
@@ -749,15 +1006,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="4">
+        <v>46191</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J11">
         <v>0</v>
       </c>
@@ -767,15 +1034,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="H12" s="4">
+        <v>46197</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="J12">
         <v>0</v>
       </c>
@@ -785,15 +1062,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="4">
+        <v>46197</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="J13">
         <v>0</v>
       </c>
@@ -803,15 +1090,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="4">
+        <v>46186</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J14">
         <v>0</v>
       </c>
@@ -821,15 +1118,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="4">
+        <v>46186</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J15">
         <v>0</v>
       </c>
@@ -839,15 +1146,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="4">
+        <v>46192</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="J16">
         <v>0</v>
       </c>
@@ -857,15 +1174,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="4">
+        <v>46192</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J17">
         <v>0</v>
       </c>
@@ -875,15 +1202,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="4">
+        <v>46197</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J18">
         <v>0</v>
       </c>
@@ -893,15 +1230,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="4">
+        <v>46197</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J19">
         <v>0</v>
       </c>
@@ -911,15 +1258,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="4">
+        <v>46185</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J20">
         <v>0</v>
       </c>
@@ -929,15 +1286,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="4">
+        <v>46187</v>
+      </c>
+      <c r="I21" s="5">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="J21">
         <v>0</v>
       </c>
@@ -947,15 +1314,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="4">
+        <v>46192</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="J22">
         <v>0</v>
       </c>
@@ -965,15 +1342,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="4">
+        <v>46192</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0.8125</v>
+      </c>
       <c r="J23">
         <v>0</v>
       </c>
@@ -983,15 +1370,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="4">
+        <v>46198</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="J24">
         <v>0</v>
       </c>
@@ -1001,15 +1398,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="4">
+        <v>46198</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="J25">
         <v>0</v>
       </c>
@@ -1019,15 +1426,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="4">
+        <v>46187</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="J26">
         <v>0</v>
       </c>
@@ -1037,15 +1454,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="4">
+        <v>46187</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="J27">
         <v>0</v>
       </c>
@@ -1055,15 +1482,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="4">
+        <v>46193</v>
+      </c>
+      <c r="I28" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J28">
         <v>0</v>
       </c>
@@ -1073,15 +1510,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="4">
+        <v>46193</v>
+      </c>
+      <c r="I29" s="5">
+        <v>0.875</v>
+      </c>
       <c r="J29">
         <v>0</v>
       </c>
@@ -1091,15 +1538,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="4">
+        <v>46198</v>
+      </c>
+      <c r="I30" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J30">
         <v>0</v>
       </c>
@@ -1109,15 +1566,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="4">
+        <v>46198</v>
+      </c>
+      <c r="I31" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J31">
         <v>0</v>
       </c>
@@ -1127,15 +1594,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="4">
+        <v>46187</v>
+      </c>
+      <c r="I32" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J32">
         <v>0</v>
       </c>
@@ -1145,15 +1622,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="4">
+        <v>46187</v>
+      </c>
+      <c r="I33" s="5">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="J33">
         <v>0</v>
       </c>
@@ -1163,15 +1650,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="4">
+        <v>46193</v>
+      </c>
+      <c r="I34" s="5">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="J34">
         <v>0</v>
       </c>
@@ -1181,15 +1678,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H35" s="4">
+        <v>46193</v>
+      </c>
+      <c r="I35" s="5">
+        <v>0.85416666666666663</v>
+      </c>
       <c r="J35">
         <v>0</v>
       </c>
@@ -1199,15 +1706,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="4">
+        <v>46198</v>
+      </c>
+      <c r="I36" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J36">
         <v>0</v>
       </c>
@@ -1217,15 +1734,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="4">
+        <v>46198</v>
+      </c>
+      <c r="I37" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J37">
         <v>0</v>
       </c>
@@ -1235,15 +1762,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H38" s="4">
+        <v>46188</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J38">
         <v>0</v>
       </c>
@@ -1253,15 +1790,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H39" s="4">
+        <v>46188</v>
+      </c>
+      <c r="I39" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J39">
         <v>0</v>
       </c>
@@ -1271,15 +1818,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="4">
+        <v>46194</v>
+      </c>
+      <c r="I40" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J40">
         <v>0</v>
       </c>
@@ -1289,15 +1846,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="4">
+        <v>46194</v>
+      </c>
+      <c r="I41" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J41">
         <v>0</v>
       </c>
@@ -1307,15 +1874,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H42" s="4">
+        <v>46199</v>
+      </c>
+      <c r="I42" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J42">
         <v>0</v>
       </c>
@@ -1325,15 +1902,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" s="4">
+        <v>46199</v>
+      </c>
+      <c r="I43" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J43">
         <v>0</v>
       </c>
@@ -1343,15 +1930,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" s="4">
+        <v>46188</v>
+      </c>
+      <c r="I44" s="5">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="J44">
         <v>0</v>
       </c>
@@ -1361,15 +1958,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H45" s="4">
+        <v>46188</v>
+      </c>
+      <c r="I45" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J45">
         <v>0</v>
       </c>
@@ -1379,15 +1986,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H46" s="4">
+        <v>46194</v>
+      </c>
+      <c r="I46" s="5">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="J46">
         <v>0</v>
       </c>
@@ -1397,15 +2014,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" s="4">
+        <v>46194</v>
+      </c>
+      <c r="I47" s="5">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="J47">
         <v>0</v>
       </c>
@@ -1415,15 +2042,25 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H48" s="4">
+        <v>46199</v>
+      </c>
+      <c r="I48" s="5">
+        <v>0.875</v>
+      </c>
       <c r="J48">
         <v>0</v>
       </c>
@@ -1433,15 +2070,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H49" s="4">
+        <v>46199</v>
+      </c>
+      <c r="I49" s="5">
+        <v>0.875</v>
+      </c>
       <c r="J49">
         <v>0</v>
       </c>
@@ -1451,15 +2098,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H50" s="4">
+        <v>46189</v>
+      </c>
+      <c r="I50" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J50">
         <v>0</v>
       </c>
@@ -1469,15 +2126,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51" s="4">
+        <v>46189</v>
+      </c>
+      <c r="I51" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J51">
         <v>0</v>
       </c>
@@ -1487,15 +2154,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H52" s="4">
+        <v>46195</v>
+      </c>
+      <c r="I52" s="5">
+        <v>0.75</v>
+      </c>
       <c r="J52">
         <v>0</v>
       </c>
@@ -1505,15 +2182,25 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H53" s="4">
+        <v>46195</v>
+      </c>
+      <c r="I53" s="5">
+        <v>0.6875</v>
+      </c>
       <c r="J53">
         <v>0</v>
       </c>
@@ -1523,15 +2210,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H54" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I54" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J54">
         <v>0</v>
       </c>
@@ -1541,15 +2238,25 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H55" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I55" s="5">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J55">
         <v>0</v>
       </c>
@@ -1559,15 +2266,25 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H56" s="4">
+        <v>46189</v>
+      </c>
+      <c r="I56" s="5">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="J56">
         <v>0</v>
       </c>
@@ -1577,15 +2294,25 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H57" s="4">
+        <v>46190</v>
+      </c>
+      <c r="I57" s="5">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="J57">
         <v>0</v>
       </c>
@@ -1595,15 +2322,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H58" s="4">
+        <v>46195</v>
+      </c>
+      <c r="I58" s="5">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="J58">
         <v>0</v>
       </c>
@@ -1613,15 +2350,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H59" s="4">
+        <v>46195</v>
+      </c>
+      <c r="I59" s="5">
+        <v>0.8125</v>
+      </c>
       <c r="J59">
         <v>0</v>
       </c>
@@ -1631,15 +2378,25 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H60" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I60" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J60">
         <v>0</v>
       </c>
@@ -1649,15 +2406,25 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H61" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I61" s="5">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J61">
         <v>0</v>
       </c>
@@ -1667,15 +2434,25 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H62" s="4">
+        <v>46190</v>
+      </c>
+      <c r="I62" s="5">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="J62">
         <v>0</v>
       </c>
@@ -1685,15 +2462,25 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H63" s="4">
+        <v>46190</v>
+      </c>
+      <c r="I63" s="5">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="J63">
         <v>0</v>
       </c>
@@ -1703,15 +2490,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H64" s="4">
+        <v>46196</v>
+      </c>
+      <c r="I64" s="5">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="J64">
         <v>0</v>
       </c>
@@ -1721,15 +2518,25 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H65" s="4">
+        <v>46196</v>
+      </c>
+      <c r="I65" s="5">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="J65">
         <v>0</v>
       </c>
@@ -1739,15 +2546,25 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H66" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I66" s="5">
+        <v>0.9375</v>
+      </c>
       <c r="J66">
         <v>0</v>
       </c>
@@ -1757,15 +2574,25 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H67" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I67" s="5">
+        <v>0.9375</v>
+      </c>
       <c r="J67">
         <v>0</v>
       </c>
@@ -1775,15 +2602,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H68" s="4">
+        <v>46190</v>
+      </c>
+      <c r="I68" s="5">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="J68">
         <v>0</v>
       </c>
@@ -1793,15 +2630,25 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="4">
+        <v>46190</v>
+      </c>
+      <c r="I69" s="5">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="J69">
         <v>0</v>
       </c>
@@ -1811,15 +2658,25 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H70" s="4">
+        <v>46196</v>
+      </c>
+      <c r="I70" s="5">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="J70">
         <v>0</v>
       </c>
@@ -1829,15 +2686,25 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" s="4">
+        <v>46196</v>
+      </c>
+      <c r="I71" s="5">
+        <v>0.64583333333333337</v>
+      </c>
       <c r="J71">
         <v>0</v>
       </c>
@@ -1847,15 +2714,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H72" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I72" s="5">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="J72">
         <v>0</v>
       </c>
@@ -1865,15 +2742,25 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H73" s="4">
+        <v>46200</v>
+      </c>
+      <c r="I73" s="5">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="J73">
         <v>0</v>
       </c>
@@ -1893,31 +2780,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1925,7 +2812,7 @@
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1936,7 +2823,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1947,7 +2834,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1958,7 +2845,7 @@
         <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1969,7 +2856,7 @@
         <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1980,7 +2867,7 @@
         <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1991,7 +2878,7 @@
         <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2002,7 +2889,7 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2013,7 +2900,7 @@
         <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2024,7 +2911,7 @@
         <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2035,7 +2922,7 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2046,7 +2933,7 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2057,7 +2944,7 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2068,7 +2955,7 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2079,7 +2966,7 @@
         <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2090,7 +2977,7 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2101,7 +2988,7 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2112,7 +2999,7 @@
         <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2123,7 +3010,7 @@
         <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2134,7 +3021,7 @@
         <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2145,7 +3032,7 @@
         <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2156,7 +3043,7 @@
         <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2167,7 +3054,7 @@
         <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -2178,7 +3065,7 @@
         <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2189,7 +3076,7 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2200,7 +3087,7 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2211,7 +3098,7 @@
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2222,7 +3109,7 @@
         <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2233,7 +3120,7 @@
         <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2244,7 +3131,7 @@
         <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2255,7 +3142,7 @@
         <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -2266,7 +3153,7 @@
         <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J33">
         <v>0</v>
